--- a/public/files/CHR/ev_join.xlsx
+++ b/public/files/CHR/ev_join.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\user\.antigravity\game\files\CHR\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{34B68DA1-2F01-42EF-8599-4A19C7390026}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{838D8564-9BF3-4714-A06B-0EF5A5847B81}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="2025" yWindow="555" windowWidth="26205" windowHeight="14850" xr2:uid="{C0E8C2FE-F33F-4C68-94BE-01501C7913C0}"/>
+    <workbookView xWindow="900" yWindow="615" windowWidth="26205" windowHeight="14850" activeTab="9" xr2:uid="{C0E8C2FE-F33F-4C68-94BE-01501C7913C0}"/>
   </bookViews>
   <sheets>
     <sheet name="4ノア" sheetId="9" r:id="rId1"/>
@@ -22,6 +22,7 @@
     <sheet name="14李乃果" sheetId="5" r:id="rId7"/>
     <sheet name="Sheet1" sheetId="6" r:id="rId8"/>
     <sheet name="確認表" sheetId="1" r:id="rId9"/>
+    <sheet name="5リフィエル" sheetId="10" r:id="rId10"/>
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
@@ -33,7 +34,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="378" uniqueCount="355">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="421" uniqueCount="397">
   <si>
     <t>愚者</t>
     <rPh sb="0" eb="2">
@@ -103,10 +104,6 @@
     <rPh sb="0" eb="2">
       <t>キョウコウ</t>
     </rPh>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
-    <t>ミランダ</t>
     <phoneticPr fontId="1"/>
   </si>
   <si>
@@ -1744,6 +1741,145 @@
     </rPh>
     <rPh sb="10" eb="11">
       <t>ナカ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>リフィエル</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>——ふと、視界の端に何かが揺れた。</t>
+  </si>
+  <si>
+    <t>蝶、だろうか。</t>
+  </si>
+  <si>
+    <t>淡く発光するような羽が、瓦礫の隙間から差し込むわずかな光を受けて、七色に揺らめいている。あまりに幻想的な羽ばたきに、紫苑は思わず目で追ってしまった。</t>
+  </si>
+  <si>
+    <t>その"蝶"は、紫苑の視線に気づいたのか、迷いのない軌道でこちらへとひらひらと近づいてくる。</t>
+  </si>
+  <si>
+    <t>そして、目の前で止まった。</t>
+  </si>
+  <si>
+    <t>蝶ではなかった。</t>
+  </si>
+  <si>
+    <t>小さな人の形をした何か——長い金色の髪、尖った耳、透き通る羽。それが、宙に浮いたまま、紫苑をまっすぐに見つめていた。</t>
+  </si>
+  <si>
+    <t>その声は、鈴を転がすように軽やかだった。</t>
+  </si>
+  <si>
+    <t>リフィエル「……私の姿が見える方に出会えて、嬉しいです」</t>
+  </si>
+  <si>
+    <t>紫苑は、しばらく言葉を失っていた。木々に呑まれた化け物や、得体の知れない何かばかりを見てきたこの数ヶ月で、こんなにも穏やかな存在に出会ったのは初めてだったからかもしれない。</t>
+  </si>
+  <si>
+    <t>紫苑「……妖精さん……か。……私は、紫苑といいます」</t>
+  </si>
+  <si>
+    <t>名乗りながら、紫苑はゆっくりと体を起こした。警戒よりも先に、ある種の安堵に似た感情が湧いてくる。</t>
+  </si>
+  <si>
+    <t>紫苑「教えて。……この世界は、何なの」</t>
+  </si>
+  <si>
+    <t>すがるような響きが、自分でも意外なほど声に滲んでいた。</t>
+  </si>
+  <si>
+    <t>リフィエルは、少し困ったように微笑んだ。</t>
+  </si>
+  <si>
+    <t>リフィエル「……ごめんなさい。私も、突然この世界に迷い込んでしまって……分からないのです」</t>
+  </si>
+  <si>
+    <t>その答えに、紫苑は小さく息を吐いた。</t>
+  </si>
+  <si>
+    <t>紫苑「……そうか」</t>
+  </si>
+  <si>
+    <t>期待していなかったと言えば嘘になる。だが、それ以上に——誰かと、こうして言葉を交わせていること自体が、久しく忘れていた感覚だった。</t>
+  </si>
+  <si>
+    <t>紫苑は、そのまま力なくうなだれる。</t>
+  </si>
+  <si>
+    <t>紫苑「……ちょっと、疲れちゃった」</t>
+  </si>
+  <si>
+    <t>そう呟いてから、紫苑はふと顔を上げ、目の前の小さな妖精を見た。</t>
+  </si>
+  <si>
+    <t>紫苑「……リフィ……エル、さん? は、何か……魔法とか、使えたりするの?」</t>
+  </si>
+  <si>
+    <t>縋るような、それでいてどこか自嘲めいた問いだった。頼れるものなら、どんな些細なものでもいい——そんな本音が透けて見える。</t>
+  </si>
+  <si>
+    <t>リフィエルは、羽を小さく震わせながら、少し申し訳なさそうに首を振った。</t>
+  </si>
+  <si>
+    <t>リフィエル「私自身には、大した力はありません。……ただ、ほんの少しだけ、異次元の力……ごくわずかに、世界の法則を変える力を、お借りすることができるのです」</t>
+  </si>
+  <si>
+    <t>紫苑「……」</t>
+  </si>
+  <si>
+    <t>その言葉の意味を、すぐには飲み込めなかった。ただ、リフィエルの表情には、誇張でも謙遜でもない、静かな確信のようなものがあった。</t>
+  </si>
+  <si>
+    <t>リフィエル「それは、私自身にはさしたる力を発揮しません。……けれど、紫苑さんのような方であれば」</t>
+  </si>
+  <si>
+    <t>リフィエルは、そこで一度言葉を切り、紫苑をまっすぐに見つめた。</t>
+  </si>
+  <si>
+    <t>リフィエル「その僅かな変化さえも、大きな力に変えられるかもしれません」</t>
+  </si>
+  <si>
+    <t>紫苑は、その小さな体をしばらく見つめ返していた。信じるに足る根拠など、どこにもない。それでも——</t>
+  </si>
+  <si>
+    <t>紫苑は、静かに頷いた。</t>
+  </si>
+  <si>
+    <t>紫苑「この先、どうなるか分からないけど……それでも、一緒に来てくれるかい?」</t>
+  </si>
+  <si>
+    <t>差し出したのは、手ではなく、言葉だった。それでも、その意味するところは同じだった。</t>
+  </si>
+  <si>
+    <t>リフィエルの表情が、ぱっと明るくなる。羽が、喜びを表すように小さく震えた。</t>
+  </si>
+  <si>
+    <t>リフィエル「はい……! ぜひ、お願いします!」</t>
+  </si>
+  <si>
+    <t>その声には、迷いも警戒もなかった。ただ純粋な喜びだけが、そこにあった。</t>
+  </si>
+  <si>
+    <t>紫苑は、初めて——少しだけ、口元を緩めた。</t>
+  </si>
+  <si>
+    <t>紫苑は崩れた壁にもたれ、束の間の休息を取っていた。浅く息をついている。</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>??？「こんにちは。……私は妖精のリフィエルと申します」</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>[背景：ヘクス背景　 BGM：JOIN_US.mp3]</t>
+    <rPh sb="1" eb="3">
+      <t>ハイケイ</t>
+    </rPh>
+    <rPh sb="7" eb="9">
+      <t>ハイケイ</t>
     </rPh>
     <phoneticPr fontId="1"/>
   </si>
@@ -2242,177 +2378,403 @@
   <sheetData>
     <row r="1" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A1" t="s">
-        <v>178</v>
+        <v>177</v>
       </c>
     </row>
     <row r="2" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A2" t="s">
-        <v>322</v>
+        <v>321</v>
       </c>
     </row>
     <row r="4" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A4" t="s">
-        <v>354</v>
+        <v>353</v>
       </c>
     </row>
     <row r="6" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A6" t="s">
-        <v>239</v>
+        <v>238</v>
       </c>
     </row>
     <row r="8" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A8" t="s">
-        <v>323</v>
+        <v>322</v>
       </c>
     </row>
     <row r="10" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A10" t="s">
-        <v>324</v>
+        <v>323</v>
       </c>
     </row>
     <row r="12" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A12" t="s">
-        <v>325</v>
+        <v>324</v>
       </c>
     </row>
     <row r="14" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A14" t="s">
-        <v>326</v>
+        <v>325</v>
       </c>
     </row>
     <row r="16" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A16" t="s">
-        <v>327</v>
+        <v>326</v>
       </c>
     </row>
     <row r="18" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A18" t="s">
-        <v>328</v>
+        <v>327</v>
       </c>
     </row>
     <row r="20" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A20" t="s">
-        <v>329</v>
+        <v>328</v>
       </c>
     </row>
     <row r="22" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A22" t="s">
-        <v>330</v>
+        <v>329</v>
       </c>
     </row>
     <row r="24" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A24" t="s">
-        <v>331</v>
+        <v>330</v>
       </c>
     </row>
     <row r="26" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A26" t="s">
-        <v>332</v>
+        <v>331</v>
       </c>
     </row>
     <row r="28" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A28" t="s">
-        <v>333</v>
+        <v>332</v>
       </c>
     </row>
     <row r="30" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A30" t="s">
-        <v>334</v>
+        <v>333</v>
       </c>
     </row>
     <row r="32" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A32" t="s">
-        <v>335</v>
+        <v>334</v>
       </c>
     </row>
     <row r="34" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A34" t="s">
-        <v>336</v>
+        <v>335</v>
       </c>
     </row>
     <row r="36" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A36" t="s">
-        <v>337</v>
+        <v>336</v>
       </c>
     </row>
     <row r="38" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A38" t="s">
-        <v>338</v>
+        <v>337</v>
       </c>
     </row>
     <row r="40" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A40" t="s">
-        <v>339</v>
+        <v>338</v>
       </c>
     </row>
     <row r="42" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A42" t="s">
-        <v>340</v>
+        <v>339</v>
       </c>
     </row>
     <row r="44" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A44" t="s">
-        <v>341</v>
+        <v>340</v>
       </c>
     </row>
     <row r="46" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A46" t="s">
-        <v>342</v>
+        <v>341</v>
       </c>
     </row>
     <row r="48" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A48" t="s">
-        <v>343</v>
+        <v>342</v>
       </c>
     </row>
     <row r="50" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A50" t="s">
-        <v>344</v>
+        <v>343</v>
       </c>
     </row>
     <row r="52" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A52" t="s">
-        <v>345</v>
+        <v>344</v>
       </c>
     </row>
     <row r="54" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A54" t="s">
-        <v>346</v>
+        <v>345</v>
       </c>
     </row>
     <row r="56" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A56" t="s">
-        <v>347</v>
+        <v>346</v>
       </c>
     </row>
     <row r="58" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A58" t="s">
-        <v>348</v>
+        <v>347</v>
       </c>
     </row>
     <row r="60" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A60" t="s">
-        <v>349</v>
+        <v>348</v>
       </c>
     </row>
     <row r="62" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A62" t="s">
-        <v>350</v>
+        <v>349</v>
       </c>
     </row>
     <row r="64" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A64" t="s">
-        <v>351</v>
+        <v>350</v>
       </c>
     </row>
     <row r="66" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A66" t="s">
-        <v>352</v>
+        <v>351</v>
       </c>
     </row>
     <row r="68" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A68" t="s">
-        <v>353</v>
+        <v>352</v>
+      </c>
+    </row>
+  </sheetData>
+  <phoneticPr fontId="1"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet10.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{C4296CCD-6720-4E4F-B8BB-828AD5777B7E}">
+  <dimension ref="A1:A85"/>
+  <sheetFormatPr defaultRowHeight="18.75" x14ac:dyDescent="0.4"/>
+  <sheetData>
+    <row r="1" spans="1:1" x14ac:dyDescent="0.4">
+      <c r="A1" s="2" t="s">
+        <v>396</v>
+      </c>
+    </row>
+    <row r="3" spans="1:1" x14ac:dyDescent="0.4">
+      <c r="A3" t="s">
+        <v>394</v>
+      </c>
+    </row>
+    <row r="5" spans="1:1" x14ac:dyDescent="0.4">
+      <c r="A5" t="s">
+        <v>355</v>
+      </c>
+    </row>
+    <row r="7" spans="1:1" x14ac:dyDescent="0.4">
+      <c r="A7" t="s">
+        <v>356</v>
+      </c>
+    </row>
+    <row r="9" spans="1:1" x14ac:dyDescent="0.4">
+      <c r="A9" t="s">
+        <v>357</v>
+      </c>
+    </row>
+    <row r="11" spans="1:1" x14ac:dyDescent="0.4">
+      <c r="A11" t="s">
+        <v>358</v>
+      </c>
+    </row>
+    <row r="13" spans="1:1" x14ac:dyDescent="0.4">
+      <c r="A13" t="s">
+        <v>359</v>
+      </c>
+    </row>
+    <row r="15" spans="1:1" x14ac:dyDescent="0.4">
+      <c r="A15" t="s">
+        <v>360</v>
+      </c>
+    </row>
+    <row r="17" spans="1:1" x14ac:dyDescent="0.4">
+      <c r="A17" t="s">
+        <v>361</v>
+      </c>
+    </row>
+    <row r="19" spans="1:1" x14ac:dyDescent="0.4">
+      <c r="A19" t="s">
+        <v>395</v>
+      </c>
+    </row>
+    <row r="21" spans="1:1" x14ac:dyDescent="0.4">
+      <c r="A21" t="s">
+        <v>362</v>
+      </c>
+    </row>
+    <row r="23" spans="1:1" x14ac:dyDescent="0.4">
+      <c r="A23" t="s">
+        <v>363</v>
+      </c>
+    </row>
+    <row r="25" spans="1:1" x14ac:dyDescent="0.4">
+      <c r="A25" t="s">
+        <v>364</v>
+      </c>
+    </row>
+    <row r="27" spans="1:1" x14ac:dyDescent="0.4">
+      <c r="A27" t="s">
+        <v>365</v>
+      </c>
+    </row>
+    <row r="29" spans="1:1" x14ac:dyDescent="0.4">
+      <c r="A29" t="s">
+        <v>366</v>
+      </c>
+    </row>
+    <row r="31" spans="1:1" x14ac:dyDescent="0.4">
+      <c r="A31" t="s">
+        <v>367</v>
+      </c>
+    </row>
+    <row r="33" spans="1:1" x14ac:dyDescent="0.4">
+      <c r="A33" t="s">
+        <v>368</v>
+      </c>
+    </row>
+    <row r="35" spans="1:1" x14ac:dyDescent="0.4">
+      <c r="A35" t="s">
+        <v>369</v>
+      </c>
+    </row>
+    <row r="37" spans="1:1" x14ac:dyDescent="0.4">
+      <c r="A37" t="s">
+        <v>370</v>
+      </c>
+    </row>
+    <row r="39" spans="1:1" x14ac:dyDescent="0.4">
+      <c r="A39" t="s">
+        <v>371</v>
+      </c>
+    </row>
+    <row r="41" spans="1:1" x14ac:dyDescent="0.4">
+      <c r="A41" t="s">
+        <v>372</v>
+      </c>
+    </row>
+    <row r="43" spans="1:1" x14ac:dyDescent="0.4">
+      <c r="A43" t="s">
+        <v>373</v>
+      </c>
+    </row>
+    <row r="45" spans="1:1" x14ac:dyDescent="0.4">
+      <c r="A45" t="s">
+        <v>374</v>
+      </c>
+    </row>
+    <row r="47" spans="1:1" x14ac:dyDescent="0.4">
+      <c r="A47" t="s">
+        <v>375</v>
+      </c>
+    </row>
+    <row r="49" spans="1:1" x14ac:dyDescent="0.4">
+      <c r="A49" t="s">
+        <v>376</v>
+      </c>
+    </row>
+    <row r="51" spans="1:1" x14ac:dyDescent="0.4">
+      <c r="A51" t="s">
+        <v>377</v>
+      </c>
+    </row>
+    <row r="53" spans="1:1" x14ac:dyDescent="0.4">
+      <c r="A53" t="s">
+        <v>378</v>
+      </c>
+    </row>
+    <row r="55" spans="1:1" x14ac:dyDescent="0.4">
+      <c r="A55" t="s">
+        <v>379</v>
+      </c>
+    </row>
+    <row r="57" spans="1:1" x14ac:dyDescent="0.4">
+      <c r="A57" t="s">
+        <v>380</v>
+      </c>
+    </row>
+    <row r="59" spans="1:1" x14ac:dyDescent="0.4">
+      <c r="A59" t="s">
+        <v>381</v>
+      </c>
+    </row>
+    <row r="61" spans="1:1" x14ac:dyDescent="0.4">
+      <c r="A61" t="s">
+        <v>382</v>
+      </c>
+    </row>
+    <row r="63" spans="1:1" x14ac:dyDescent="0.4">
+      <c r="A63" t="s">
+        <v>383</v>
+      </c>
+    </row>
+    <row r="65" spans="1:1" x14ac:dyDescent="0.4">
+      <c r="A65" t="s">
+        <v>384</v>
+      </c>
+    </row>
+    <row r="67" spans="1:1" x14ac:dyDescent="0.4">
+      <c r="A67" t="s">
+        <v>385</v>
+      </c>
+    </row>
+    <row r="69" spans="1:1" x14ac:dyDescent="0.4">
+      <c r="A69" t="s">
+        <v>386</v>
+      </c>
+    </row>
+    <row r="71" spans="1:1" x14ac:dyDescent="0.4">
+      <c r="A71" t="s">
+        <v>372</v>
+      </c>
+    </row>
+    <row r="73" spans="1:1" x14ac:dyDescent="0.4">
+      <c r="A73" t="s">
+        <v>387</v>
+      </c>
+    </row>
+    <row r="75" spans="1:1" x14ac:dyDescent="0.4">
+      <c r="A75" t="s">
+        <v>388</v>
+      </c>
+    </row>
+    <row r="77" spans="1:1" x14ac:dyDescent="0.4">
+      <c r="A77" t="s">
+        <v>389</v>
+      </c>
+    </row>
+    <row r="79" spans="1:1" x14ac:dyDescent="0.4">
+      <c r="A79" t="s">
+        <v>390</v>
+      </c>
+    </row>
+    <row r="81" spans="1:1" x14ac:dyDescent="0.4">
+      <c r="A81" t="s">
+        <v>391</v>
+      </c>
+    </row>
+    <row r="83" spans="1:1" x14ac:dyDescent="0.4">
+      <c r="A83" t="s">
+        <v>392</v>
+      </c>
+    </row>
+    <row r="85" spans="1:1" x14ac:dyDescent="0.4">
+      <c r="A85" t="s">
+        <v>393</v>
       </c>
     </row>
   </sheetData>
@@ -2428,237 +2790,237 @@
   <sheetData>
     <row r="1" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A1" t="s">
-        <v>178</v>
+        <v>177</v>
       </c>
     </row>
     <row r="2" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A2" s="2" t="s">
-        <v>279</v>
+        <v>278</v>
       </c>
     </row>
     <row r="3" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A3" t="s">
-        <v>280</v>
+        <v>279</v>
       </c>
     </row>
     <row r="5" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A5" t="s">
-        <v>281</v>
+        <v>280</v>
       </c>
     </row>
     <row r="7" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A7" t="s">
-        <v>237</v>
+        <v>236</v>
       </c>
     </row>
     <row r="9" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A9" t="s">
-        <v>238</v>
+        <v>237</v>
       </c>
     </row>
     <row r="11" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A11" t="s">
-        <v>239</v>
+        <v>238</v>
       </c>
     </row>
     <row r="13" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A13" t="s">
-        <v>240</v>
+        <v>239</v>
       </c>
     </row>
     <row r="15" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A15" t="s">
-        <v>241</v>
+        <v>240</v>
       </c>
     </row>
     <row r="17" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A17" t="s">
-        <v>242</v>
+        <v>241</v>
       </c>
     </row>
     <row r="19" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A19" t="s">
-        <v>243</v>
+        <v>242</v>
       </c>
     </row>
     <row r="21" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A21" t="s">
-        <v>244</v>
+        <v>243</v>
       </c>
     </row>
     <row r="23" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A23" t="s">
-        <v>245</v>
+        <v>244</v>
       </c>
     </row>
     <row r="25" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A25" t="s">
-        <v>246</v>
+        <v>245</v>
       </c>
     </row>
     <row r="27" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A27" t="s">
-        <v>247</v>
+        <v>246</v>
       </c>
     </row>
     <row r="29" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A29" t="s">
-        <v>248</v>
+        <v>247</v>
       </c>
     </row>
     <row r="31" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A31" t="s">
-        <v>249</v>
+        <v>248</v>
       </c>
     </row>
     <row r="33" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A33" t="s">
-        <v>250</v>
+        <v>249</v>
       </c>
     </row>
     <row r="35" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A35" t="s">
-        <v>251</v>
+        <v>250</v>
       </c>
     </row>
     <row r="37" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A37" t="s">
-        <v>252</v>
+        <v>251</v>
       </c>
     </row>
     <row r="39" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A39" t="s">
-        <v>253</v>
+        <v>252</v>
       </c>
     </row>
     <row r="41" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A41" t="s">
-        <v>254</v>
+        <v>253</v>
       </c>
     </row>
     <row r="43" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A43" t="s">
-        <v>255</v>
+        <v>254</v>
       </c>
     </row>
     <row r="45" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A45" t="s">
-        <v>256</v>
+        <v>255</v>
       </c>
     </row>
     <row r="47" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A47" t="s">
-        <v>257</v>
+        <v>256</v>
       </c>
     </row>
     <row r="49" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A49" t="s">
-        <v>258</v>
+        <v>257</v>
       </c>
     </row>
     <row r="51" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A51" t="s">
-        <v>259</v>
+        <v>258</v>
       </c>
     </row>
     <row r="53" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A53" t="s">
-        <v>260</v>
+        <v>259</v>
       </c>
     </row>
     <row r="55" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A55" t="s">
-        <v>261</v>
+        <v>260</v>
       </c>
     </row>
     <row r="57" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A57" t="s">
-        <v>262</v>
+        <v>261</v>
       </c>
     </row>
     <row r="59" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A59" t="s">
-        <v>263</v>
+        <v>262</v>
       </c>
     </row>
     <row r="61" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A61" t="s">
-        <v>264</v>
+        <v>263</v>
       </c>
     </row>
     <row r="63" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A63" t="s">
-        <v>265</v>
+        <v>264</v>
       </c>
     </row>
     <row r="65" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A65" t="s">
-        <v>266</v>
+        <v>265</v>
       </c>
     </row>
     <row r="67" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A67" t="s">
-        <v>267</v>
+        <v>266</v>
       </c>
     </row>
     <row r="69" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A69" t="s">
-        <v>268</v>
+        <v>267</v>
       </c>
     </row>
     <row r="71" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A71" t="s">
-        <v>269</v>
+        <v>268</v>
       </c>
     </row>
     <row r="73" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A73" t="s">
-        <v>270</v>
+        <v>269</v>
       </c>
     </row>
     <row r="75" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A75" t="s">
-        <v>271</v>
+        <v>270</v>
       </c>
     </row>
     <row r="77" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A77" t="s">
-        <v>272</v>
+        <v>271</v>
       </c>
     </row>
     <row r="79" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A79" t="s">
-        <v>273</v>
+        <v>272</v>
       </c>
     </row>
     <row r="81" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A81" t="s">
-        <v>274</v>
+        <v>273</v>
       </c>
     </row>
     <row r="83" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A83" t="s">
-        <v>275</v>
+        <v>274</v>
       </c>
     </row>
     <row r="85" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A85" t="s">
-        <v>276</v>
+        <v>275</v>
       </c>
     </row>
     <row r="87" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A87" t="s">
-        <v>277</v>
+        <v>276</v>
       </c>
     </row>
     <row r="89" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A89" t="s">
-        <v>278</v>
+        <v>277</v>
       </c>
     </row>
     <row r="91" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A91" t="s">
-        <v>282</v>
+        <v>281</v>
       </c>
     </row>
   </sheetData>
@@ -2674,202 +3036,202 @@
   <sheetData>
     <row r="1" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A1" t="s">
-        <v>178</v>
+        <v>177</v>
       </c>
     </row>
     <row r="2" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A2" t="s">
-        <v>321</v>
+        <v>320</v>
       </c>
     </row>
     <row r="4" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A4" t="s">
-        <v>283</v>
+        <v>282</v>
       </c>
     </row>
     <row r="5" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A5" t="s">
-        <v>284</v>
+        <v>283</v>
       </c>
     </row>
     <row r="6" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A6" t="s">
-        <v>285</v>
+        <v>284</v>
       </c>
     </row>
     <row r="7" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A7" t="s">
-        <v>286</v>
+        <v>285</v>
       </c>
     </row>
     <row r="9" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A9" t="s">
-        <v>287</v>
+        <v>286</v>
       </c>
     </row>
     <row r="11" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A11" t="s">
-        <v>288</v>
+        <v>287</v>
       </c>
     </row>
     <row r="12" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A12" t="s">
-        <v>289</v>
+        <v>288</v>
       </c>
     </row>
     <row r="13" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A13" t="s">
-        <v>319</v>
+        <v>318</v>
       </c>
     </row>
     <row r="15" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A15" t="s">
-        <v>320</v>
+        <v>319</v>
       </c>
     </row>
     <row r="16" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A16" t="s">
-        <v>290</v>
+        <v>289</v>
       </c>
     </row>
     <row r="17" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A17" t="s">
-        <v>291</v>
+        <v>290</v>
       </c>
     </row>
     <row r="19" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A19" t="s">
-        <v>292</v>
+        <v>291</v>
       </c>
     </row>
     <row r="20" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A20" t="s">
-        <v>293</v>
+        <v>292</v>
       </c>
     </row>
     <row r="22" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A22" t="s">
-        <v>294</v>
+        <v>293</v>
       </c>
     </row>
     <row r="23" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A23" t="s">
-        <v>295</v>
+        <v>294</v>
       </c>
     </row>
     <row r="24" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A24" t="s">
-        <v>296</v>
+        <v>295</v>
       </c>
     </row>
     <row r="26" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A26" t="s">
-        <v>297</v>
+        <v>296</v>
       </c>
     </row>
     <row r="27" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A27" t="s">
-        <v>298</v>
+        <v>297</v>
       </c>
     </row>
     <row r="28" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A28" t="s">
-        <v>299</v>
+        <v>298</v>
       </c>
     </row>
     <row r="29" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A29" t="s">
-        <v>300</v>
+        <v>299</v>
       </c>
     </row>
     <row r="30" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A30" t="s">
-        <v>301</v>
+        <v>300</v>
       </c>
     </row>
     <row r="32" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A32" t="s">
-        <v>302</v>
+        <v>301</v>
       </c>
     </row>
     <row r="33" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A33" t="s">
-        <v>303</v>
+        <v>302</v>
       </c>
     </row>
     <row r="35" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A35" t="s">
-        <v>304</v>
+        <v>303</v>
       </c>
     </row>
     <row r="36" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A36" t="s">
-        <v>305</v>
+        <v>304</v>
       </c>
     </row>
     <row r="38" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A38" t="s">
-        <v>306</v>
+        <v>305</v>
       </c>
     </row>
     <row r="39" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A39" t="s">
-        <v>307</v>
+        <v>306</v>
       </c>
     </row>
     <row r="41" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A41" t="s">
-        <v>308</v>
+        <v>307</v>
       </c>
     </row>
     <row r="42" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A42" t="s">
-        <v>309</v>
+        <v>308</v>
       </c>
     </row>
     <row r="44" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A44" t="s">
-        <v>310</v>
+        <v>309</v>
       </c>
     </row>
     <row r="45" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A45" t="s">
-        <v>311</v>
+        <v>310</v>
       </c>
     </row>
     <row r="46" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A46" t="s">
-        <v>312</v>
+        <v>311</v>
       </c>
     </row>
     <row r="47" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A47" t="s">
-        <v>313</v>
+        <v>312</v>
       </c>
     </row>
     <row r="48" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A48" t="s">
-        <v>314</v>
+        <v>313</v>
       </c>
     </row>
     <row r="49" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A49" t="s">
-        <v>315</v>
+        <v>314</v>
       </c>
     </row>
     <row r="51" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A51" t="s">
-        <v>316</v>
+        <v>315</v>
       </c>
     </row>
     <row r="52" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A52" t="s">
-        <v>317</v>
+        <v>316</v>
       </c>
     </row>
     <row r="53" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A53" t="s">
-        <v>318</v>
+        <v>317</v>
       </c>
     </row>
   </sheetData>
@@ -2885,192 +3247,192 @@
   <sheetData>
     <row r="1" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A1" t="s">
-        <v>178</v>
+        <v>177</v>
       </c>
     </row>
     <row r="2" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A2" t="s">
-        <v>233</v>
+        <v>232</v>
       </c>
     </row>
     <row r="3" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A3" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
     </row>
     <row r="4" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A4" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
     </row>
     <row r="6" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A6" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
     </row>
     <row r="8" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A8" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
     </row>
     <row r="10" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A10" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
     </row>
     <row r="11" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A11" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
     </row>
     <row r="12" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A12" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
     </row>
     <row r="14" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A14" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
     </row>
     <row r="16" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A16" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
     </row>
     <row r="18" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A18" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
     </row>
     <row r="19" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A19" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
     </row>
     <row r="21" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A21" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
     </row>
     <row r="22" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A22" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
     </row>
     <row r="23" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A23" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
     </row>
     <row r="25" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A25" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
     </row>
     <row r="26" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A26" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
     </row>
     <row r="28" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A28" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
     </row>
     <row r="30" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A30" t="s">
-        <v>136</v>
+        <v>135</v>
       </c>
     </row>
     <row r="31" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A31" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
     </row>
     <row r="32" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A32" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
     </row>
     <row r="34" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A34" t="s">
-        <v>137</v>
+        <v>136</v>
       </c>
     </row>
     <row r="35" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A35" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
     </row>
     <row r="36" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A36" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
     </row>
     <row r="38" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A38" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
     </row>
     <row r="40" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A40" t="s">
-        <v>138</v>
+        <v>137</v>
       </c>
     </row>
     <row r="41" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A41" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
     </row>
     <row r="42" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A42" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
     </row>
     <row r="44" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A44" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
     </row>
     <row r="46" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A46" t="s">
-        <v>139</v>
+        <v>138</v>
       </c>
     </row>
     <row r="47" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A47" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
     </row>
     <row r="48" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A48" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
     </row>
     <row r="49" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A49" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
     </row>
     <row r="51" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A51" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
     </row>
     <row r="53" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A53" t="s">
-        <v>140</v>
+        <v>139</v>
       </c>
     </row>
     <row r="55" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A55" t="s">
-        <v>141</v>
+        <v>140</v>
       </c>
     </row>
     <row r="56" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A56" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
     </row>
   </sheetData>
@@ -3086,177 +3448,177 @@
   <sheetData>
     <row r="1" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A1" t="s">
-        <v>178</v>
+        <v>177</v>
       </c>
     </row>
     <row r="2" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A2" s="2" t="s">
-        <v>234</v>
+        <v>233</v>
       </c>
     </row>
     <row r="3" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A3" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
     </row>
     <row r="4" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A4" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
     </row>
     <row r="6" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A6" t="s">
-        <v>142</v>
+        <v>141</v>
       </c>
     </row>
     <row r="8" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A8" t="s">
-        <v>143</v>
+        <v>142</v>
       </c>
     </row>
     <row r="9" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A9" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
     </row>
     <row r="10" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A10" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
     </row>
     <row r="12" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A12" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
     </row>
     <row r="13" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A13" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
     </row>
     <row r="15" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A15" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
     </row>
     <row r="17" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A17" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
     </row>
     <row r="18" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A18" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
     </row>
     <row r="19" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A19" s="2" t="s">
-        <v>144</v>
+        <v>143</v>
       </c>
     </row>
     <row r="20" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A20" t="s">
-        <v>145</v>
+        <v>144</v>
       </c>
     </row>
     <row r="22" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A22" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
     </row>
     <row r="24" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A24" t="s">
-        <v>146</v>
+        <v>145</v>
       </c>
     </row>
     <row r="25" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A25" t="s">
-        <v>106</v>
+        <v>105</v>
       </c>
     </row>
     <row r="27" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A27" t="s">
-        <v>152</v>
+        <v>151</v>
       </c>
     </row>
     <row r="29" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A29" t="s">
-        <v>147</v>
+        <v>146</v>
       </c>
     </row>
     <row r="31" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A31" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
     </row>
     <row r="33" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A33" t="s">
-        <v>148</v>
+        <v>147</v>
       </c>
     </row>
     <row r="34" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A34" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
     </row>
     <row r="36" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A36" t="s">
-        <v>153</v>
+        <v>152</v>
       </c>
     </row>
     <row r="38" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A38" t="s">
-        <v>149</v>
+        <v>148</v>
       </c>
     </row>
     <row r="39" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A39" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
     </row>
     <row r="40" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A40" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
     </row>
     <row r="41" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A41" t="s">
-        <v>111</v>
+        <v>110</v>
       </c>
     </row>
     <row r="43" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A43" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
     </row>
     <row r="45" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A45" t="s">
-        <v>150</v>
+        <v>149</v>
       </c>
     </row>
     <row r="46" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A46" t="s">
-        <v>113</v>
+        <v>112</v>
       </c>
     </row>
     <row r="47" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A47" t="s">
-        <v>114</v>
+        <v>113</v>
       </c>
     </row>
     <row r="49" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A49" t="s">
-        <v>115</v>
+        <v>114</v>
       </c>
     </row>
     <row r="51" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A51" t="s">
-        <v>151</v>
+        <v>150</v>
       </c>
     </row>
     <row r="52" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A52" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
     </row>
   </sheetData>
@@ -3272,192 +3634,192 @@
   <sheetData>
     <row r="1" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A1" t="s">
-        <v>178</v>
+        <v>177</v>
       </c>
     </row>
     <row r="2" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A2" s="2" t="s">
-        <v>235</v>
+        <v>234</v>
       </c>
     </row>
     <row r="3" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A3" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
     </row>
     <row r="4" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A4" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
     </row>
     <row r="5" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A5" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
     </row>
     <row r="7" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A7" t="s">
-        <v>154</v>
+        <v>153</v>
       </c>
     </row>
     <row r="8" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A8" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
     </row>
     <row r="11" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A11" t="s">
-        <v>165</v>
+        <v>164</v>
       </c>
     </row>
     <row r="13" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A13" t="s">
-        <v>155</v>
+        <v>154</v>
       </c>
     </row>
     <row r="14" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A14" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
     </row>
     <row r="16" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A16" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
     </row>
     <row r="17" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A17" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
     </row>
     <row r="19" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A19" t="s">
-        <v>156</v>
+        <v>155</v>
       </c>
     </row>
     <row r="20" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A20" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
     </row>
     <row r="22" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A22" t="s">
-        <v>162</v>
+        <v>161</v>
       </c>
     </row>
     <row r="24" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A24" t="s">
-        <v>157</v>
+        <v>156</v>
       </c>
     </row>
     <row r="25" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A25" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
     </row>
     <row r="27" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A27" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
     </row>
     <row r="28" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A28" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
     </row>
     <row r="30" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A30" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
     </row>
     <row r="31" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A31" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
     </row>
     <row r="33" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A33" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
     </row>
     <row r="34" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A34" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
     </row>
     <row r="36" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A36" t="s">
-        <v>163</v>
+        <v>162</v>
       </c>
     </row>
     <row r="38" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A38" t="s">
-        <v>158</v>
+        <v>157</v>
       </c>
     </row>
     <row r="39" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A39" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
     </row>
     <row r="41" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A41" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
     </row>
     <row r="42" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A42" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
     </row>
     <row r="44" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A44" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
     </row>
     <row r="45" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A45" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
     </row>
     <row r="47" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A47" t="s">
-        <v>159</v>
+        <v>158</v>
       </c>
     </row>
     <row r="48" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A48" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
     </row>
     <row r="50" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A50" t="s">
-        <v>164</v>
+        <v>163</v>
       </c>
     </row>
     <row r="52" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A52" t="s">
-        <v>160</v>
+        <v>159</v>
       </c>
     </row>
     <row r="53" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A53" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
     </row>
     <row r="55" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A55" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
     </row>
     <row r="57" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A57" t="s">
-        <v>161</v>
+        <v>160</v>
       </c>
     </row>
     <row r="58" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A58" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
     </row>
   </sheetData>
@@ -3473,167 +3835,167 @@
   <sheetData>
     <row r="1" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A1" t="s">
-        <v>178</v>
+        <v>177</v>
       </c>
     </row>
     <row r="2" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A2" s="2" t="s">
-        <v>236</v>
+        <v>235</v>
       </c>
     </row>
     <row r="3" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A3" t="s">
-        <v>117</v>
+        <v>116</v>
       </c>
     </row>
     <row r="5" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A5" t="s">
-        <v>118</v>
+        <v>117</v>
       </c>
     </row>
     <row r="6" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A6" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
     </row>
     <row r="8" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A8" t="s">
-        <v>120</v>
+        <v>119</v>
       </c>
     </row>
     <row r="10" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A10" t="s">
-        <v>166</v>
+        <v>165</v>
       </c>
     </row>
     <row r="11" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A11" t="s">
-        <v>121</v>
+        <v>120</v>
       </c>
     </row>
     <row r="13" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A13" t="s">
-        <v>122</v>
+        <v>121</v>
       </c>
     </row>
     <row r="15" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A15" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
     </row>
     <row r="17" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A17" t="s">
-        <v>167</v>
+        <v>166</v>
       </c>
     </row>
     <row r="19" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A19" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
     </row>
     <row r="21" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A21" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
     </row>
     <row r="22" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A22" t="s">
-        <v>126</v>
+        <v>125</v>
       </c>
     </row>
     <row r="23" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A23" t="s">
-        <v>127</v>
+        <v>126</v>
       </c>
     </row>
     <row r="26" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A26" t="s">
-        <v>168</v>
+        <v>167</v>
       </c>
     </row>
     <row r="28" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A28" t="s">
-        <v>128</v>
+        <v>127</v>
       </c>
     </row>
     <row r="30" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A30" t="s">
-        <v>129</v>
+        <v>128</v>
       </c>
     </row>
     <row r="31" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A31" t="s">
-        <v>130</v>
+        <v>129</v>
       </c>
     </row>
     <row r="32" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A32" t="s">
-        <v>169</v>
+        <v>168</v>
       </c>
     </row>
     <row r="34" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A34" t="s">
-        <v>131</v>
+        <v>130</v>
       </c>
     </row>
     <row r="35" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A35" t="s">
-        <v>132</v>
+        <v>131</v>
       </c>
     </row>
     <row r="37" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A37" t="s">
-        <v>177</v>
+        <v>176</v>
       </c>
     </row>
     <row r="39" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A39" t="s">
-        <v>176</v>
+        <v>175</v>
       </c>
     </row>
     <row r="40" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A40" t="s">
-        <v>133</v>
+        <v>132</v>
       </c>
     </row>
     <row r="42" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A42" t="s">
-        <v>172</v>
+        <v>171</v>
       </c>
     </row>
     <row r="43" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A43" t="s">
-        <v>134</v>
+        <v>133</v>
       </c>
     </row>
     <row r="45" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A45" t="s">
-        <v>173</v>
+        <v>172</v>
       </c>
     </row>
     <row r="47" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A47" t="s">
-        <v>171</v>
+        <v>170</v>
       </c>
     </row>
     <row r="49" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A49" t="s">
-        <v>174</v>
+        <v>173</v>
       </c>
     </row>
     <row r="51" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A51" t="s">
-        <v>170</v>
+        <v>169</v>
       </c>
     </row>
     <row r="53" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A53" t="s">
-        <v>175</v>
+        <v>174</v>
       </c>
     </row>
     <row r="55" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A55" t="s">
-        <v>170</v>
+        <v>169</v>
       </c>
     </row>
   </sheetData>
@@ -3649,129 +4011,129 @@
   <sheetData>
     <row r="1" spans="1:20" ht="30" x14ac:dyDescent="0.4">
       <c r="A1" s="3" t="s">
-        <v>179</v>
+        <v>178</v>
       </c>
       <c r="K1" t="s">
-        <v>200</v>
+        <v>199</v>
       </c>
       <c r="T1" t="s">
-        <v>221</v>
+        <v>220</v>
       </c>
     </row>
     <row r="2" spans="1:20" x14ac:dyDescent="0.4">
       <c r="A2" s="4"/>
       <c r="K2" t="s">
-        <v>201</v>
+        <v>200</v>
       </c>
       <c r="T2" t="s">
-        <v>222</v>
+        <v>221</v>
       </c>
     </row>
     <row r="3" spans="1:20" x14ac:dyDescent="0.4">
       <c r="A3" s="5" t="s">
-        <v>180</v>
+        <v>179</v>
       </c>
       <c r="K3" t="s">
-        <v>202</v>
+        <v>201</v>
       </c>
       <c r="T3" t="s">
-        <v>223</v>
+        <v>222</v>
       </c>
     </row>
     <row r="4" spans="1:20" x14ac:dyDescent="0.4">
       <c r="A4" s="4"/>
       <c r="K4" t="s">
-        <v>203</v>
+        <v>202</v>
       </c>
       <c r="T4" t="s">
-        <v>224</v>
+        <v>223</v>
       </c>
     </row>
     <row r="5" spans="1:20" ht="23.25" x14ac:dyDescent="0.4">
       <c r="A5" s="6" t="s">
-        <v>181</v>
+        <v>180</v>
       </c>
       <c r="K5" t="s">
-        <v>204</v>
+        <v>203</v>
       </c>
       <c r="T5" t="s">
-        <v>225</v>
+        <v>224</v>
       </c>
     </row>
     <row r="6" spans="1:20" x14ac:dyDescent="0.4">
       <c r="A6" s="4"/>
       <c r="K6" t="s">
-        <v>205</v>
+        <v>204</v>
       </c>
       <c r="T6" t="s">
-        <v>226</v>
+        <v>225</v>
       </c>
     </row>
     <row r="7" spans="1:20" x14ac:dyDescent="0.4">
       <c r="A7" s="7" t="s">
-        <v>194</v>
+        <v>193</v>
       </c>
     </row>
     <row r="8" spans="1:20" x14ac:dyDescent="0.4">
       <c r="A8" s="8"/>
       <c r="T8" t="s">
-        <v>227</v>
+        <v>226</v>
       </c>
     </row>
     <row r="9" spans="1:20" x14ac:dyDescent="0.4">
       <c r="A9" s="9" t="s">
-        <v>182</v>
+        <v>181</v>
       </c>
       <c r="T9" t="s">
-        <v>228</v>
+        <v>227</v>
       </c>
     </row>
     <row r="10" spans="1:20" x14ac:dyDescent="0.4">
       <c r="A10" s="9" t="s">
-        <v>183</v>
+        <v>182</v>
       </c>
       <c r="T10" t="s">
-        <v>229</v>
+        <v>228</v>
       </c>
     </row>
     <row r="11" spans="1:20" x14ac:dyDescent="0.4">
       <c r="A11" s="4"/>
       <c r="T11" t="s">
-        <v>230</v>
+        <v>229</v>
       </c>
     </row>
     <row r="12" spans="1:20" x14ac:dyDescent="0.4">
       <c r="A12" s="7" t="s">
-        <v>184</v>
+        <v>183</v>
       </c>
     </row>
     <row r="13" spans="1:20" x14ac:dyDescent="0.4">
       <c r="A13" s="8"/>
       <c r="T13" t="s">
-        <v>231</v>
+        <v>230</v>
       </c>
     </row>
     <row r="14" spans="1:20" x14ac:dyDescent="0.4">
       <c r="A14" s="9" t="s">
-        <v>185</v>
+        <v>184</v>
       </c>
       <c r="T14" t="s">
-        <v>232</v>
+        <v>231</v>
       </c>
     </row>
     <row r="15" spans="1:20" x14ac:dyDescent="0.4">
       <c r="A15" s="9" t="s">
-        <v>186</v>
+        <v>185</v>
       </c>
     </row>
     <row r="16" spans="1:20" x14ac:dyDescent="0.4">
       <c r="A16" s="10" t="s">
-        <v>195</v>
+        <v>194</v>
       </c>
     </row>
     <row r="17" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A17" s="11" t="s">
-        <v>196</v>
+        <v>195</v>
       </c>
     </row>
     <row r="18" spans="1:1" x14ac:dyDescent="0.4">
@@ -3779,7 +4141,7 @@
     </row>
     <row r="19" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A19" s="7" t="s">
-        <v>187</v>
+        <v>186</v>
       </c>
     </row>
     <row r="20" spans="1:1" x14ac:dyDescent="0.4">
@@ -3787,12 +4149,12 @@
     </row>
     <row r="21" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A21" s="9" t="s">
-        <v>188</v>
+        <v>187</v>
       </c>
     </row>
     <row r="22" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A22" s="9" t="s">
-        <v>197</v>
+        <v>196</v>
       </c>
     </row>
     <row r="23" spans="1:1" x14ac:dyDescent="0.4">
@@ -3800,7 +4162,7 @@
     </row>
     <row r="24" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A24" s="7" t="s">
-        <v>189</v>
+        <v>188</v>
       </c>
     </row>
     <row r="25" spans="1:1" x14ac:dyDescent="0.4">
@@ -3808,12 +4170,12 @@
     </row>
     <row r="26" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A26" s="9" t="s">
-        <v>190</v>
+        <v>189</v>
       </c>
     </row>
     <row r="27" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A27" s="9" t="s">
-        <v>198</v>
+        <v>197</v>
       </c>
     </row>
     <row r="28" spans="1:1" ht="19.5" thickBot="1" x14ac:dyDescent="0.45">
@@ -3821,22 +4183,22 @@
     </row>
     <row r="29" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A29" s="5" t="s">
-        <v>191</v>
+        <v>190</v>
       </c>
     </row>
     <row r="30" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A30" s="13" t="s">
-        <v>193</v>
+        <v>192</v>
       </c>
     </row>
     <row r="31" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A31" s="5" t="s">
-        <v>199</v>
+        <v>198</v>
       </c>
     </row>
     <row r="32" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A32" s="5" t="s">
-        <v>192</v>
+        <v>191</v>
       </c>
     </row>
   </sheetData>
@@ -3859,19 +4221,19 @@
   <sheetData>
     <row r="1" spans="1:5" x14ac:dyDescent="0.4">
       <c r="A1" t="s">
+        <v>217</v>
+      </c>
+      <c r="B1" s="1" t="s">
         <v>218</v>
       </c>
-      <c r="B1" s="1" t="s">
+      <c r="C1" s="1" t="s">
         <v>219</v>
       </c>
-      <c r="C1" s="1" t="s">
-        <v>220</v>
-      </c>
       <c r="D1" s="1" t="s">
-        <v>215</v>
+        <v>214</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>206</v>
+        <v>205</v>
       </c>
     </row>
     <row r="2" spans="1:5" x14ac:dyDescent="0.4">
@@ -3888,7 +4250,7 @@
         <v>5</v>
       </c>
       <c r="E2" s="1" t="s">
-        <v>207</v>
+        <v>206</v>
       </c>
     </row>
     <row r="3" spans="1:5" x14ac:dyDescent="0.4">
@@ -3905,7 +4267,7 @@
         <v>5</v>
       </c>
       <c r="E3" s="1" t="s">
-        <v>208</v>
+        <v>207</v>
       </c>
     </row>
     <row r="4" spans="1:5" x14ac:dyDescent="0.4">
@@ -3922,7 +4284,7 @@
         <v>5</v>
       </c>
       <c r="E4" s="1" t="s">
-        <v>208</v>
+        <v>207</v>
       </c>
     </row>
     <row r="5" spans="1:5" x14ac:dyDescent="0.4">
@@ -3939,7 +4301,7 @@
         <v>1</v>
       </c>
       <c r="E5" s="1" t="s">
-        <v>209</v>
+        <v>208</v>
       </c>
     </row>
     <row r="6" spans="1:5" x14ac:dyDescent="0.4">
@@ -3956,7 +4318,7 @@
         <v>5</v>
       </c>
       <c r="E6" s="1" t="s">
-        <v>208</v>
+        <v>207</v>
       </c>
     </row>
     <row r="7" spans="1:5" x14ac:dyDescent="0.4">
@@ -3967,13 +4329,13 @@
         <v>10</v>
       </c>
       <c r="C7" s="1" t="s">
-        <v>11</v>
+        <v>354</v>
       </c>
       <c r="D7" s="14">
         <v>5</v>
       </c>
       <c r="E7" s="1" t="s">
-        <v>208</v>
+        <v>207</v>
       </c>
     </row>
     <row r="8" spans="1:5" x14ac:dyDescent="0.4">
@@ -3981,16 +4343,16 @@
         <v>6</v>
       </c>
       <c r="B8" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="C8" s="1" t="s">
         <v>12</v>
-      </c>
-      <c r="C8" s="1" t="s">
-        <v>13</v>
       </c>
       <c r="D8" s="14">
         <v>4</v>
       </c>
       <c r="E8" s="1" t="s">
-        <v>210</v>
+        <v>209</v>
       </c>
     </row>
     <row r="9" spans="1:5" x14ac:dyDescent="0.4">
@@ -3998,16 +4360,16 @@
         <v>7</v>
       </c>
       <c r="B9" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="C9" s="1" t="s">
         <v>14</v>
-      </c>
-      <c r="C9" s="1" t="s">
-        <v>15</v>
       </c>
       <c r="D9" s="14">
         <v>4</v>
       </c>
       <c r="E9" s="1" t="s">
-        <v>210</v>
+        <v>209</v>
       </c>
     </row>
     <row r="10" spans="1:5" x14ac:dyDescent="0.4">
@@ -4015,16 +4377,16 @@
         <v>8</v>
       </c>
       <c r="B10" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="C10" s="1" t="s">
         <v>16</v>
-      </c>
-      <c r="C10" s="1" t="s">
-        <v>17</v>
       </c>
       <c r="D10" s="14">
         <v>1</v>
       </c>
       <c r="E10" s="1" t="s">
-        <v>209</v>
+        <v>208</v>
       </c>
     </row>
     <row r="11" spans="1:5" x14ac:dyDescent="0.4">
@@ -4032,16 +4394,16 @@
         <v>9</v>
       </c>
       <c r="B11" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="C11" s="1" t="s">
         <v>18</v>
-      </c>
-      <c r="C11" s="1" t="s">
-        <v>19</v>
       </c>
       <c r="D11" s="14">
         <v>2</v>
       </c>
       <c r="E11" s="1" t="s">
-        <v>211</v>
+        <v>210</v>
       </c>
     </row>
     <row r="12" spans="1:5" x14ac:dyDescent="0.4">
@@ -4049,16 +4411,16 @@
         <v>10</v>
       </c>
       <c r="B12" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="C12" s="1" t="s">
         <v>20</v>
-      </c>
-      <c r="C12" s="1" t="s">
-        <v>21</v>
       </c>
       <c r="D12" s="14">
         <v>1</v>
       </c>
       <c r="E12" s="1" t="s">
-        <v>212</v>
+        <v>211</v>
       </c>
     </row>
     <row r="13" spans="1:5" x14ac:dyDescent="0.4">
@@ -4066,16 +4428,16 @@
         <v>11</v>
       </c>
       <c r="B13" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="C13" s="1" t="s">
         <v>22</v>
-      </c>
-      <c r="C13" s="1" t="s">
-        <v>23</v>
       </c>
       <c r="D13" s="14">
         <v>1</v>
       </c>
       <c r="E13" s="1" t="s">
-        <v>209</v>
+        <v>208</v>
       </c>
     </row>
     <row r="14" spans="1:5" x14ac:dyDescent="0.4">
@@ -4083,16 +4445,16 @@
         <v>12</v>
       </c>
       <c r="B14" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="C14" s="1" t="s">
         <v>24</v>
-      </c>
-      <c r="C14" s="1" t="s">
-        <v>25</v>
       </c>
       <c r="D14" s="14">
         <v>4</v>
       </c>
       <c r="E14" s="1" t="s">
-        <v>210</v>
+        <v>209</v>
       </c>
     </row>
     <row r="15" spans="1:5" x14ac:dyDescent="0.4">
@@ -4100,16 +4462,16 @@
         <v>13</v>
       </c>
       <c r="B15" s="1" t="s">
+        <v>25</v>
+      </c>
+      <c r="C15" s="1" t="s">
         <v>26</v>
-      </c>
-      <c r="C15" s="1" t="s">
-        <v>27</v>
       </c>
       <c r="D15" s="14">
         <v>4</v>
       </c>
       <c r="E15" s="1" t="s">
-        <v>210</v>
+        <v>209</v>
       </c>
     </row>
     <row r="16" spans="1:5" x14ac:dyDescent="0.4">
@@ -4117,16 +4479,16 @@
         <v>14</v>
       </c>
       <c r="B16" s="1" t="s">
+        <v>27</v>
+      </c>
+      <c r="C16" s="1" t="s">
         <v>28</v>
-      </c>
-      <c r="C16" s="1" t="s">
-        <v>29</v>
       </c>
       <c r="D16" s="14">
         <v>2</v>
       </c>
       <c r="E16" s="1" t="s">
-        <v>211</v>
+        <v>210</v>
       </c>
     </row>
     <row r="17" spans="1:5" x14ac:dyDescent="0.4">
@@ -4134,16 +4496,16 @@
         <v>15</v>
       </c>
       <c r="B17" s="1" t="s">
+        <v>29</v>
+      </c>
+      <c r="C17" s="1" t="s">
         <v>30</v>
-      </c>
-      <c r="C17" s="1" t="s">
-        <v>31</v>
       </c>
       <c r="D17" s="14">
         <v>4</v>
       </c>
       <c r="E17" s="1" t="s">
-        <v>210</v>
+        <v>209</v>
       </c>
     </row>
     <row r="18" spans="1:5" x14ac:dyDescent="0.4">
@@ -4151,16 +4513,16 @@
         <v>16</v>
       </c>
       <c r="B18" s="1" t="s">
+        <v>31</v>
+      </c>
+      <c r="C18" s="1" t="s">
         <v>32</v>
-      </c>
-      <c r="C18" s="1" t="s">
-        <v>33</v>
       </c>
       <c r="D18" s="14">
         <v>3</v>
       </c>
       <c r="E18" s="1" t="s">
-        <v>213</v>
+        <v>212</v>
       </c>
     </row>
     <row r="19" spans="1:5" x14ac:dyDescent="0.4">
@@ -4168,16 +4530,16 @@
         <v>17</v>
       </c>
       <c r="B19" s="1" t="s">
+        <v>33</v>
+      </c>
+      <c r="C19" s="1" t="s">
         <v>34</v>
-      </c>
-      <c r="C19" s="1" t="s">
-        <v>35</v>
       </c>
       <c r="D19" s="14">
         <v>5</v>
       </c>
       <c r="E19" s="1" t="s">
-        <v>208</v>
+        <v>207</v>
       </c>
     </row>
     <row r="20" spans="1:5" x14ac:dyDescent="0.4">
@@ -4185,16 +4547,16 @@
         <v>18</v>
       </c>
       <c r="B20" s="1" t="s">
+        <v>35</v>
+      </c>
+      <c r="C20" s="1" t="s">
         <v>36</v>
-      </c>
-      <c r="C20" s="1" t="s">
-        <v>37</v>
       </c>
       <c r="D20" s="14">
         <v>4</v>
       </c>
       <c r="E20" s="1" t="s">
-        <v>210</v>
+        <v>209</v>
       </c>
     </row>
     <row r="21" spans="1:5" x14ac:dyDescent="0.4">
@@ -4202,16 +4564,16 @@
         <v>19</v>
       </c>
       <c r="B21" s="1" t="s">
+        <v>37</v>
+      </c>
+      <c r="C21" s="1" t="s">
         <v>38</v>
-      </c>
-      <c r="C21" s="1" t="s">
-        <v>39</v>
       </c>
       <c r="D21" s="14">
         <v>4</v>
       </c>
       <c r="E21" s="1" t="s">
-        <v>210</v>
+        <v>209</v>
       </c>
     </row>
     <row r="22" spans="1:5" x14ac:dyDescent="0.4">
@@ -4219,16 +4581,16 @@
         <v>20</v>
       </c>
       <c r="B22" s="1" t="s">
+        <v>39</v>
+      </c>
+      <c r="C22" s="1" t="s">
         <v>40</v>
-      </c>
-      <c r="C22" s="1" t="s">
-        <v>41</v>
       </c>
       <c r="D22" s="14">
         <v>4</v>
       </c>
       <c r="E22" s="1" t="s">
-        <v>214</v>
+        <v>213</v>
       </c>
     </row>
     <row r="23" spans="1:5" x14ac:dyDescent="0.4">
@@ -4236,26 +4598,26 @@
         <v>21</v>
       </c>
       <c r="B23" s="1" t="s">
+        <v>41</v>
+      </c>
+      <c r="C23" s="1" t="s">
         <v>42</v>
-      </c>
-      <c r="C23" s="1" t="s">
-        <v>43</v>
       </c>
       <c r="D23" s="14">
         <v>5</v>
       </c>
       <c r="E23" s="1" t="s">
-        <v>208</v>
+        <v>207</v>
       </c>
     </row>
     <row r="25" spans="1:5" x14ac:dyDescent="0.4">
       <c r="A25" t="s">
-        <v>216</v>
+        <v>215</v>
       </c>
     </row>
     <row r="26" spans="1:5" x14ac:dyDescent="0.4">
       <c r="A26" t="s">
-        <v>217</v>
+        <v>216</v>
       </c>
     </row>
   </sheetData>
